--- a/artfynd/S 462-2023 artfynd.xlsx
+++ b/artfynd/S 462-2023 artfynd.xlsx
@@ -1009,7 +1009,7 @@
         <v>136357765</v>
       </c>
       <c r="B5" t="n">
-        <v>92902</v>
+        <v>92905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 462-2023 artfynd.xlsx
+++ b/artfynd/S 462-2023 artfynd.xlsx
@@ -1009,7 +1009,7 @@
         <v>136357765</v>
       </c>
       <c r="B5" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 462-2023 artfynd.xlsx
+++ b/artfynd/S 462-2023 artfynd.xlsx
@@ -1009,7 +1009,7 @@
         <v>136357765</v>
       </c>
       <c r="B5" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 462-2023 artfynd.xlsx
+++ b/artfynd/S 462-2023 artfynd.xlsx
@@ -1009,7 +1009,7 @@
         <v>136357765</v>
       </c>
       <c r="B5" t="n">
-        <v>92911</v>
+        <v>92913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 462-2023 artfynd.xlsx
+++ b/artfynd/S 462-2023 artfynd.xlsx
@@ -1009,7 +1009,7 @@
         <v>136357765</v>
       </c>
       <c r="B5" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 462-2023 artfynd.xlsx
+++ b/artfynd/S 462-2023 artfynd.xlsx
@@ -1009,7 +1009,7 @@
         <v>136357765</v>
       </c>
       <c r="B5" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
